--- a/Soccer/step8_soccer_direction_clean.xlsx
+++ b/Soccer/step8_soccer_direction_clean.xlsx
@@ -3461,7 +3461,7 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
@@ -3586,21 +3586,21 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Renan Peixoto</t>
+          <t>Alejandro García</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Attacker</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>FWD</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
@@ -3623,10 +3623,14 @@
           <t>03/29 6:30 PM</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr"/>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>268187</t>
+        </is>
+      </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>Assists</t>
+          <t>Goal + Assist</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
@@ -3651,10 +3655,10 @@
         <v>-0.5</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="S22" s="3" t="inlineStr"/>
       <c r="T22" s="3" t="inlineStr"/>
@@ -3711,17 +3715,17 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Alejandro García</t>
+          <t>Renan Peixoto</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Attacker</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -3744,14 +3748,10 @@
           <t>03/29 6:30 PM</t>
         </is>
       </c>
-      <c r="J23" s="6" t="inlineStr">
-        <is>
-          <t>268187</t>
-        </is>
-      </c>
+      <c r="J23" s="6" t="inlineStr"/>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>Goal + Assist</t>
+          <t>Assists</t>
         </is>
       </c>
       <c r="L23" s="6" t="inlineStr">
@@ -3776,10 +3776,10 @@
         <v>-0.5</v>
       </c>
       <c r="Q23" s="6" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="R23" s="6" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="S23" s="6" t="inlineStr"/>
       <c r="T23" s="6" t="inlineStr"/>
@@ -4078,7 +4078,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
@@ -4227,26 +4227,26 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Jordan Barrera</t>
+          <t>Steven Mendoza</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Attacker</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>BOTAFOGO</t>
+          <t>ATHLETICO PR</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
@@ -4266,12 +4266,12 @@
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>360063</t>
+          <t>197049</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>Shots On Target</t>
+          <t>Goals</t>
         </is>
       </c>
       <c r="L27" s="6" t="inlineStr">
@@ -4290,25 +4290,25 @@
         </is>
       </c>
       <c r="O27" s="6" t="n">
-        <v>-0.17</v>
+        <v>0</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="Q27" s="6" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="R27" s="6" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="S27" s="6" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="T27" s="6" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="U27" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V27" s="6" t="n">
         <v>2</v>
@@ -4342,10 +4342,14 @@
       </c>
       <c r="AD27" s="6" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE27" s="6" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE27" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AF27" s="6" t="inlineStr"/>
       <c r="AG27" s="6" t="inlineStr"/>
       <c r="AH27" s="6" t="inlineStr"/>
@@ -4354,7 +4358,7 @@
       <c r="AK27" s="6" t="inlineStr"/>
       <c r="AL27" s="6" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="AM27" s="6" t="inlineStr"/>
@@ -4380,22 +4384,22 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Steven Mendoza</t>
+          <t>Jordan Barrera</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Attacker</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>FWD</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>ATHLETICO PR</t>
+          <t>BOTAFOGO</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -4415,12 +4419,12 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>197049</t>
+          <t>360063</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>Goals</t>
+          <t>Shots On Target</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
@@ -4439,25 +4443,25 @@
         </is>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>2</v>
@@ -4491,14 +4495,10 @@
       </c>
       <c r="AD28" s="3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE28" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE28" s="3" t="inlineStr"/>
       <c r="AF28" s="3" t="inlineStr"/>
       <c r="AG28" s="3" t="inlineStr"/>
       <c r="AH28" s="3" t="inlineStr"/>
@@ -4507,7 +4507,7 @@
       <c r="AK28" s="3" t="inlineStr"/>
       <c r="AL28" s="3" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="AM28" s="3" t="inlineStr"/>
@@ -29115,7 +29115,7 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
@@ -29240,21 +29240,21 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Renan Peixoto</t>
+          <t>Alejandro García</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Attacker</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>FWD</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
@@ -29277,10 +29277,14 @@
           <t>03/29 6:30 PM</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr"/>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>268187</t>
+        </is>
+      </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>Assists</t>
+          <t>Goal + Assist</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
@@ -29305,10 +29309,10 @@
         <v>-0.5</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="S22" s="3" t="inlineStr"/>
       <c r="T22" s="3" t="inlineStr"/>
@@ -29365,17 +29369,17 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Alejandro García</t>
+          <t>Renan Peixoto</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Attacker</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -29398,14 +29402,10 @@
           <t>03/29 6:30 PM</t>
         </is>
       </c>
-      <c r="J23" s="6" t="inlineStr">
-        <is>
-          <t>268187</t>
-        </is>
-      </c>
+      <c r="J23" s="6" t="inlineStr"/>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>Goal + Assist</t>
+          <t>Assists</t>
         </is>
       </c>
       <c r="L23" s="6" t="inlineStr">
@@ -29430,10 +29430,10 @@
         <v>-0.5</v>
       </c>
       <c r="Q23" s="6" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="R23" s="6" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="S23" s="6" t="inlineStr"/>
       <c r="T23" s="6" t="inlineStr"/>
@@ -29997,7 +29997,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
@@ -30146,26 +30146,26 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>Jordan Barrera</t>
+          <t>Steven Mendoza</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Attacker</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>BOTAFOGO</t>
+          <t>ATHLETICO PR</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
@@ -30185,12 +30185,12 @@
       </c>
       <c r="J3" s="6" t="inlineStr">
         <is>
-          <t>360063</t>
+          <t>197049</t>
         </is>
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>Shots On Target</t>
+          <t>Goals</t>
         </is>
       </c>
       <c r="L3" s="6" t="inlineStr">
@@ -30209,25 +30209,25 @@
         </is>
       </c>
       <c r="O3" s="6" t="n">
-        <v>-0.17</v>
+        <v>0</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="Q3" s="6" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="R3" s="6" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="S3" s="6" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="T3" s="6" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="U3" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V3" s="6" t="n">
         <v>2</v>
@@ -30261,10 +30261,14 @@
       </c>
       <c r="AD3" s="6" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE3" s="6" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE3" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AF3" s="6" t="inlineStr"/>
       <c r="AG3" s="6" t="inlineStr"/>
       <c r="AH3" s="6" t="inlineStr"/>
@@ -30273,7 +30277,7 @@
       <c r="AK3" s="6" t="inlineStr"/>
       <c r="AL3" s="6" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="AM3" s="6" t="inlineStr"/>
@@ -30299,22 +30303,22 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Steven Mendoza</t>
+          <t>Jordan Barrera</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Attacker</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>FWD</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>ATHLETICO PR</t>
+          <t>BOTAFOGO</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -30334,12 +30338,12 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>197049</t>
+          <t>360063</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Goals</t>
+          <t>Shots On Target</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -30358,25 +30362,25 @@
         </is>
       </c>
       <c r="O4" s="3" t="n">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V4" s="3" t="n">
         <v>2</v>
@@ -30410,14 +30414,10 @@
       </c>
       <c r="AD4" s="3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE4" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE4" s="3" t="inlineStr"/>
       <c r="AF4" s="3" t="inlineStr"/>
       <c r="AG4" s="3" t="inlineStr"/>
       <c r="AH4" s="3" t="inlineStr"/>
@@ -30426,7 +30426,7 @@
       <c r="AK4" s="3" t="inlineStr"/>
       <c r="AL4" s="3" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="AM4" s="3" t="inlineStr"/>

--- a/Soccer/step8_soccer_direction_clean.xlsx
+++ b/Soccer/step8_soccer_direction_clean.xlsx
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5.57</v>
+        <v>5.58</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
@@ -954,21 +954,21 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>4.15</v>
+        <v>4.11</v>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>Raul</t>
+          <t>Danilo</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>Goalkeeper</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>GK</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
@@ -993,22 +993,22 @@
       </c>
       <c r="J3" s="6" t="inlineStr">
         <is>
-          <t>233826</t>
+          <t>306764</t>
         </is>
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>Goalie Saves</t>
+          <t>Shots</t>
         </is>
       </c>
       <c r="L3" s="6" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Goblin</t>
         </is>
       </c>
       <c r="M3" s="6" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="N3" s="5" t="inlineStr">
@@ -1017,19 +1017,19 @@
         </is>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1.83</v>
+        <v>0.83</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>4.33</v>
+        <v>1.33</v>
       </c>
       <c r="Q3" s="6" t="n">
-        <v>0.9006999999999999</v>
+        <v>0.9144</v>
       </c>
       <c r="R3" s="6" t="n">
-        <v>0.0386</v>
+        <v>0.2174</v>
       </c>
       <c r="S3" s="6" t="n">
-        <v>0.9702</v>
+        <v>0.9743000000000001</v>
       </c>
       <c r="T3" s="6" t="n">
         <v>1</v>
@@ -1038,10 +1038,10 @@
         <v>1</v>
       </c>
       <c r="V3" s="6" t="n">
-        <v>4.3</v>
+        <v>1.3</v>
       </c>
       <c r="W3" s="6" t="n">
-        <v>4.3</v>
+        <v>1.3</v>
       </c>
       <c r="X3" s="6" t="n">
         <v>3</v>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="AB3" s="6" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MID_VOL</t>
         </is>
       </c>
       <c r="AC3" s="6" t="inlineStr">
@@ -1072,17 +1072,17 @@
       <c r="AD3" s="6" t="inlineStr"/>
       <c r="AE3" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF3" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AG3" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AH3" s="6" t="inlineStr"/>
@@ -1094,7 +1094,7 @@
       <c r="AN3" s="6" t="inlineStr"/>
       <c r="AO3" s="6" t="inlineStr">
         <is>
-          <t>4.333</t>
+          <t>1.333</t>
         </is>
       </c>
       <c r="AP3" s="6" t="inlineStr"/>
@@ -1116,33 +1116,33 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>4.1</v>
+        <v>3.74</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Danilo</t>
+          <t>Willian Machado</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
+          <t>MIRASSOL</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
           <t>BOTAFOGO</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>MIRASSOL</t>
-        </is>
-      </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
           <t>SOCCER</t>
@@ -1155,22 +1155,22 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>306764</t>
+          <t>270797</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Shots</t>
+          <t>Passes Attempted</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>Goblin</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>60.5</t>
         </is>
       </c>
       <c r="N4" s="5" t="inlineStr">
@@ -1179,41 +1179,33 @@
         </is>
       </c>
       <c r="O4" s="3" t="n">
-        <v>0.83</v>
+        <v>0</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>1.33</v>
+        <v>60.5</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.9144</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.2174</v>
+        <v>-0.4339</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.9743000000000001</v>
+        <v>0.4538</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>1</v>
+        <v>0.62</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="V4" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W4" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X4" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y4" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>0.62</v>
+      </c>
+      <c r="V4" s="3" t="inlineStr"/>
+      <c r="W4" s="3" t="inlineStr"/>
+      <c r="X4" s="3" t="inlineStr"/>
+      <c r="Y4" s="3" t="inlineStr"/>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr">
@@ -1223,30 +1215,18 @@
       </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t>MID_VOL</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
-          <t>FRINGE</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AD4" s="3" t="inlineStr"/>
-      <c r="AE4" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AF4" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AG4" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="AE4" s="3" t="inlineStr"/>
+      <c r="AF4" s="3" t="inlineStr"/>
+      <c r="AG4" s="3" t="inlineStr"/>
       <c r="AH4" s="3" t="inlineStr"/>
       <c r="AI4" s="3" t="inlineStr"/>
       <c r="AJ4" s="3" t="inlineStr"/>
@@ -1254,11 +1234,7 @@
       <c r="AL4" s="3" t="inlineStr"/>
       <c r="AM4" s="3" t="inlineStr"/>
       <c r="AN4" s="3" t="inlineStr"/>
-      <c r="AO4" s="3" t="inlineStr">
-        <is>
-          <t>1.333</t>
-        </is>
-      </c>
+      <c r="AO4" s="3" t="inlineStr"/>
       <c r="AP4" s="3" t="inlineStr"/>
       <c r="AQ4" s="3" t="inlineStr">
         <is>
@@ -1278,33 +1254,33 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>3.74</v>
+        <v>3.64</v>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Willian Machado</t>
+          <t>Raul</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Goalkeeper</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
+          <t>BOTAFOGO</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
           <t>MIRASSOL</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>BOTAFOGO</t>
-        </is>
-      </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
           <t>SOCCER</t>
@@ -1317,12 +1293,12 @@
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>270797</t>
+          <t>233826</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>Passes Attempted</t>
+          <t>Goalie Saves</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
@@ -1332,7 +1308,7 @@
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
-          <t>60.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N5" s="5" t="inlineStr">
@@ -1341,33 +1317,41 @@
         </is>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>60.5</v>
+        <v>4.33</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.9063</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>-0.4339</v>
+        <v>0.115</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>0.4538</v>
+        <v>0.9719</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>0.62</v>
+        <v>1</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="V5" s="6" t="inlineStr"/>
-      <c r="W5" s="6" t="inlineStr"/>
-      <c r="X5" s="6" t="inlineStr"/>
-      <c r="Y5" s="6" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V5" s="6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="W5" s="6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="X5" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y5" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="Z5" s="6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AA5" s="6" t="inlineStr">
@@ -1382,13 +1366,25 @@
       </c>
       <c r="AC5" s="6" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>FRINGE</t>
         </is>
       </c>
       <c r="AD5" s="6" t="inlineStr"/>
-      <c r="AE5" s="6" t="inlineStr"/>
-      <c r="AF5" s="6" t="inlineStr"/>
-      <c r="AG5" s="6" t="inlineStr"/>
+      <c r="AE5" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AF5" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AG5" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="AH5" s="6" t="inlineStr"/>
       <c r="AI5" s="6" t="inlineStr"/>
       <c r="AJ5" s="6" t="inlineStr"/>
@@ -1396,7 +1392,11 @@
       <c r="AL5" s="6" t="inlineStr"/>
       <c r="AM5" s="6" t="inlineStr"/>
       <c r="AN5" s="6" t="inlineStr"/>
-      <c r="AO5" s="6" t="inlineStr"/>
+      <c r="AO5" s="6" t="inlineStr">
+        <is>
+          <t>4.333</t>
+        </is>
+      </c>
       <c r="AP5" s="6" t="inlineStr"/>
       <c r="AQ5" s="6" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>3.37</v>
+        <v>3.38</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
@@ -5670,17 +5670,17 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Igor Formiga</t>
+          <t>Lucas Mugni</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
@@ -5703,10 +5703,14 @@
           <t>04/01 6:30 PM</t>
         </is>
       </c>
-      <c r="J35" s="6" t="inlineStr"/>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>147148</t>
+        </is>
+      </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>Shots On Target</t>
+          <t>Assists</t>
         </is>
       </c>
       <c r="L35" s="6" t="inlineStr">
@@ -5716,7 +5720,7 @@
       </c>
       <c r="M35" s="6" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="N35" s="5" t="inlineStr">
@@ -5725,25 +5729,25 @@
         </is>
       </c>
       <c r="O35" s="6" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="P35" s="6" t="n">
         <v>-0.5</v>
       </c>
       <c r="Q35" s="6" t="n">
-        <v>0.0579</v>
+        <v>0.0569</v>
       </c>
       <c r="R35" s="6" t="n">
-        <v>-0.0613</v>
+        <v>-0.2121</v>
       </c>
       <c r="S35" s="6" t="n">
-        <v>0.3254</v>
+        <v>0.3391</v>
       </c>
       <c r="T35" s="6" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="U35" s="6" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="V35" s="6" t="inlineStr"/>
       <c r="W35" s="6" t="inlineStr"/>
@@ -5800,21 +5804,21 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Lucas Mugni</t>
+          <t>Igor Formiga</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
@@ -5837,11 +5841,7 @@
           <t>04/01 6:30 PM</t>
         </is>
       </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>147148</t>
-        </is>
-      </c>
+      <c r="J36" s="3" t="inlineStr"/>
       <c r="K36" s="3" t="inlineStr">
         <is>
           <t>Assists</t>
@@ -5938,7 +5938,7 @@
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
       <c r="J37" s="6" t="inlineStr"/>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>Assists</t>
+          <t>Shots On Target</t>
         </is>
       </c>
       <c r="L37" s="6" t="inlineStr">
@@ -5988,7 +5988,7 @@
       </c>
       <c r="M37" s="6" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="N37" s="5" t="inlineStr">
@@ -5997,25 +5997,25 @@
         </is>
       </c>
       <c r="O37" s="6" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="P37" s="6" t="n">
         <v>-0.5</v>
       </c>
       <c r="Q37" s="6" t="n">
-        <v>0.0569</v>
+        <v>0.0579</v>
       </c>
       <c r="R37" s="6" t="n">
-        <v>-0.2121</v>
+        <v>-0.0613</v>
       </c>
       <c r="S37" s="6" t="n">
-        <v>0.3391</v>
+        <v>0.3254</v>
       </c>
       <c r="T37" s="6" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="U37" s="6" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="V37" s="6" t="inlineStr"/>
       <c r="W37" s="6" t="inlineStr"/>
@@ -7386,7 +7386,7 @@
         </is>
       </c>
       <c r="B47" s="6" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
@@ -8676,7 +8676,7 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
@@ -10104,7 +10104,7 @@
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
@@ -10242,7 +10242,7 @@
         </is>
       </c>
       <c r="B67" s="6" t="n">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
@@ -12364,7 +12364,7 @@
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
@@ -17146,7 +17146,7 @@
         </is>
       </c>
       <c r="B109" s="6" t="n">
-        <v>-0.46</v>
+        <v>-0.47</v>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>Antonio Galeano</t>
+          <t>Nathan Fogaça</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
@@ -17355,12 +17355,12 @@
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
-          <t>254464</t>
+          <t>273399</t>
         </is>
       </c>
       <c r="K110" s="3" t="inlineStr">
         <is>
-          <t>Assists</t>
+          <t>Shots</t>
         </is>
       </c>
       <c r="L110" s="3" t="inlineStr">
@@ -17370,7 +17370,7 @@
       </c>
       <c r="M110" s="3" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="N110" s="5" t="inlineStr">
@@ -17379,19 +17379,19 @@
         </is>
       </c>
       <c r="O110" s="3" t="n">
-        <v>-0.5</v>
+        <v>-4.25</v>
       </c>
       <c r="P110" s="3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>0.056</v>
+        <v>0.0554</v>
       </c>
       <c r="R110" s="3" t="n">
-        <v>-0.3215</v>
+        <v>0.0414</v>
       </c>
       <c r="S110" s="3" t="n">
-        <v>0.0168</v>
+        <v>0.0166</v>
       </c>
       <c r="T110" s="3" t="n">
         <v>0</v>
@@ -17400,10 +17400,10 @@
         <v>0</v>
       </c>
       <c r="V110" s="3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W110" s="3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X110" s="3" t="n">
         <v>0</v>
@@ -17423,7 +17423,7 @@
       </c>
       <c r="AB110" s="3" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>LOW_VOL</t>
         </is>
       </c>
       <c r="AC110" s="3" t="inlineStr">
@@ -17443,17 +17443,17 @@
       </c>
       <c r="AF110" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AG110" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AH110" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI110" s="3" t="inlineStr"/>
@@ -17464,7 +17464,7 @@
       <c r="AN110" s="3" t="inlineStr"/>
       <c r="AO110" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AP110" s="3" t="inlineStr"/>
@@ -17486,11 +17486,11 @@
         </is>
       </c>
       <c r="B111" s="6" t="n">
-        <v>-0.48</v>
+        <v>-0.49</v>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>Carlos Eduardo</t>
+          <t>Antonio Galeano</t>
         </is>
       </c>
       <c r="D111" s="6" t="inlineStr">
@@ -17525,7 +17525,7 @@
       </c>
       <c r="J111" s="6" t="inlineStr">
         <is>
-          <t>350244</t>
+          <t>254464</t>
         </is>
       </c>
       <c r="K111" s="6" t="inlineStr">
@@ -17579,7 +17579,7 @@
         <v>0</v>
       </c>
       <c r="Y111" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z111" s="6" t="inlineStr">
         <is>
@@ -17621,7 +17621,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AH111" s="6" t="inlineStr"/>
+      <c r="AH111" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AI111" s="6" t="inlineStr"/>
       <c r="AJ111" s="6" t="inlineStr"/>
       <c r="AK111" s="6" t="inlineStr"/>
@@ -17652,11 +17656,11 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>-0.48</v>
+        <v>-0.49</v>
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>Tiquinho Soares</t>
+          <t>Carlos Eduardo</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
@@ -17691,7 +17695,7 @@
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
-          <t>202374</t>
+          <t>350244</t>
         </is>
       </c>
       <c r="K112" s="3" t="inlineStr">
@@ -17818,11 +17822,11 @@
         </is>
       </c>
       <c r="B113" s="6" t="n">
-        <v>-0.48</v>
+        <v>-0.49</v>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>Nathan Fogaça</t>
+          <t>Tiquinho Soares</t>
         </is>
       </c>
       <c r="D113" s="6" t="inlineStr">
@@ -17857,7 +17861,7 @@
       </c>
       <c r="J113" s="6" t="inlineStr">
         <is>
-          <t>273399</t>
+          <t>202374</t>
         </is>
       </c>
       <c r="K113" s="6" t="inlineStr">
@@ -17911,7 +17915,7 @@
         <v>0</v>
       </c>
       <c r="Y113" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z113" s="6" t="inlineStr">
         <is>
@@ -17953,11 +17957,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AH113" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AH113" s="6" t="inlineStr"/>
       <c r="AI113" s="6" t="inlineStr"/>
       <c r="AJ113" s="6" t="inlineStr"/>
       <c r="AK113" s="6" t="inlineStr"/>
@@ -17988,7 +17988,7 @@
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>-0.48</v>
+        <v>-0.49</v>
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
@@ -18032,7 +18032,7 @@
       </c>
       <c r="K114" s="3" t="inlineStr">
         <is>
-          <t>Shots</t>
+          <t>Assists</t>
         </is>
       </c>
       <c r="L114" s="3" t="inlineStr">
@@ -18042,7 +18042,7 @@
       </c>
       <c r="M114" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="N114" s="5" t="inlineStr">
@@ -18051,19 +18051,19 @@
         </is>
       </c>
       <c r="O114" s="3" t="n">
-        <v>-4.25</v>
+        <v>-0.5</v>
       </c>
       <c r="P114" s="3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Q114" s="3" t="n">
-        <v>0.0554</v>
+        <v>0.056</v>
       </c>
       <c r="R114" s="3" t="n">
-        <v>0.0414</v>
+        <v>-0.3215</v>
       </c>
       <c r="S114" s="3" t="n">
-        <v>0.0166</v>
+        <v>0.0168</v>
       </c>
       <c r="T114" s="3" t="n">
         <v>0</v>
@@ -18072,10 +18072,10 @@
         <v>0</v>
       </c>
       <c r="V114" s="3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W114" s="3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X114" s="3" t="n">
         <v>0</v>
@@ -18095,7 +18095,7 @@
       </c>
       <c r="AB114" s="3" t="inlineStr">
         <is>
-          <t>LOW_VOL</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AC114" s="3" t="inlineStr">
@@ -18115,17 +18115,17 @@
       </c>
       <c r="AF114" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG114" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AH114" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AI114" s="3" t="inlineStr"/>
@@ -18136,7 +18136,7 @@
       <c r="AN114" s="3" t="inlineStr"/>
       <c r="AO114" s="3" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AP114" s="3" t="inlineStr"/>
@@ -18227,10 +18227,10 @@
         <v>0</v>
       </c>
       <c r="Q115" s="6" t="n">
-        <v>0.0563</v>
+        <v>0.0562</v>
       </c>
       <c r="R115" s="6" t="n">
-        <v>-0.1261</v>
+        <v>-0.1262</v>
       </c>
       <c r="S115" s="6" t="n">
         <v>0.0169</v>
@@ -18393,10 +18393,10 @@
         <v>0</v>
       </c>
       <c r="Q116" s="3" t="n">
-        <v>0.0563</v>
+        <v>0.0562</v>
       </c>
       <c r="R116" s="3" t="n">
-        <v>-0.1261</v>
+        <v>-0.1262</v>
       </c>
       <c r="S116" s="3" t="n">
         <v>0.0169</v>
@@ -21336,7 +21336,7 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>-0.85</v>
+        <v>-0.86</v>
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
@@ -36535,7 +36535,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5.57</v>
+        <v>5.58</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
@@ -36697,21 +36697,21 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>4.15</v>
+        <v>4.11</v>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>Raul</t>
+          <t>Danilo</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>Goalkeeper</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>GK</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
@@ -36736,22 +36736,22 @@
       </c>
       <c r="J3" s="6" t="inlineStr">
         <is>
-          <t>233826</t>
+          <t>306764</t>
         </is>
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>Goalie Saves</t>
+          <t>Shots</t>
         </is>
       </c>
       <c r="L3" s="6" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Goblin</t>
         </is>
       </c>
       <c r="M3" s="6" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="N3" s="5" t="inlineStr">
@@ -36760,19 +36760,19 @@
         </is>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1.83</v>
+        <v>0.83</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>4.33</v>
+        <v>1.33</v>
       </c>
       <c r="Q3" s="6" t="n">
-        <v>0.9006999999999999</v>
+        <v>0.9144</v>
       </c>
       <c r="R3" s="6" t="n">
-        <v>0.0386</v>
+        <v>0.2174</v>
       </c>
       <c r="S3" s="6" t="n">
-        <v>0.9702</v>
+        <v>0.9743000000000001</v>
       </c>
       <c r="T3" s="6" t="n">
         <v>1</v>
@@ -36781,10 +36781,10 @@
         <v>1</v>
       </c>
       <c r="V3" s="6" t="n">
-        <v>4.3</v>
+        <v>1.3</v>
       </c>
       <c r="W3" s="6" t="n">
-        <v>4.3</v>
+        <v>1.3</v>
       </c>
       <c r="X3" s="6" t="n">
         <v>3</v>
@@ -36804,7 +36804,7 @@
       </c>
       <c r="AB3" s="6" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MID_VOL</t>
         </is>
       </c>
       <c r="AC3" s="6" t="inlineStr">
@@ -36815,17 +36815,17 @@
       <c r="AD3" s="6" t="inlineStr"/>
       <c r="AE3" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF3" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AG3" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AH3" s="6" t="inlineStr"/>
@@ -36837,7 +36837,7 @@
       <c r="AN3" s="6" t="inlineStr"/>
       <c r="AO3" s="6" t="inlineStr">
         <is>
-          <t>4.333</t>
+          <t>1.333</t>
         </is>
       </c>
       <c r="AP3" s="6" t="inlineStr"/>
@@ -36859,33 +36859,33 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>4.1</v>
+        <v>3.74</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Danilo</t>
+          <t>Willian Machado</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
+          <t>MIRASSOL</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
           <t>BOTAFOGO</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>MIRASSOL</t>
-        </is>
-      </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
           <t>SOCCER</t>
@@ -36898,22 +36898,22 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>306764</t>
+          <t>270797</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Shots</t>
+          <t>Passes Attempted</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>Goblin</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>60.5</t>
         </is>
       </c>
       <c r="N4" s="5" t="inlineStr">
@@ -36922,41 +36922,33 @@
         </is>
       </c>
       <c r="O4" s="3" t="n">
-        <v>0.83</v>
+        <v>0</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>1.33</v>
+        <v>60.5</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.9144</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.2174</v>
+        <v>-0.4339</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.9743000000000001</v>
+        <v>0.4538</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>1</v>
+        <v>0.62</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="V4" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W4" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X4" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y4" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>0.62</v>
+      </c>
+      <c r="V4" s="3" t="inlineStr"/>
+      <c r="W4" s="3" t="inlineStr"/>
+      <c r="X4" s="3" t="inlineStr"/>
+      <c r="Y4" s="3" t="inlineStr"/>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr">
@@ -36966,30 +36958,18 @@
       </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t>MID_VOL</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
-          <t>FRINGE</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AD4" s="3" t="inlineStr"/>
-      <c r="AE4" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AF4" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AG4" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="AE4" s="3" t="inlineStr"/>
+      <c r="AF4" s="3" t="inlineStr"/>
+      <c r="AG4" s="3" t="inlineStr"/>
       <c r="AH4" s="3" t="inlineStr"/>
       <c r="AI4" s="3" t="inlineStr"/>
       <c r="AJ4" s="3" t="inlineStr"/>
@@ -36997,11 +36977,7 @@
       <c r="AL4" s="3" t="inlineStr"/>
       <c r="AM4" s="3" t="inlineStr"/>
       <c r="AN4" s="3" t="inlineStr"/>
-      <c r="AO4" s="3" t="inlineStr">
-        <is>
-          <t>1.333</t>
-        </is>
-      </c>
+      <c r="AO4" s="3" t="inlineStr"/>
       <c r="AP4" s="3" t="inlineStr"/>
       <c r="AQ4" s="3" t="inlineStr">
         <is>
@@ -37021,33 +36997,33 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>3.74</v>
+        <v>3.64</v>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Willian Machado</t>
+          <t>Raul</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Goalkeeper</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
+          <t>BOTAFOGO</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
           <t>MIRASSOL</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>BOTAFOGO</t>
-        </is>
-      </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
           <t>SOCCER</t>
@@ -37060,12 +37036,12 @@
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>270797</t>
+          <t>233826</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>Passes Attempted</t>
+          <t>Goalie Saves</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
@@ -37075,7 +37051,7 @@
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
-          <t>60.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N5" s="5" t="inlineStr">
@@ -37084,33 +37060,41 @@
         </is>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>60.5</v>
+        <v>4.33</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.9063</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>-0.4339</v>
+        <v>0.115</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>0.4538</v>
+        <v>0.9719</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>0.62</v>
+        <v>1</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="V5" s="6" t="inlineStr"/>
-      <c r="W5" s="6" t="inlineStr"/>
-      <c r="X5" s="6" t="inlineStr"/>
-      <c r="Y5" s="6" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V5" s="6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="W5" s="6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="X5" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y5" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="Z5" s="6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AA5" s="6" t="inlineStr">
@@ -37125,13 +37109,25 @@
       </c>
       <c r="AC5" s="6" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>FRINGE</t>
         </is>
       </c>
       <c r="AD5" s="6" t="inlineStr"/>
-      <c r="AE5" s="6" t="inlineStr"/>
-      <c r="AF5" s="6" t="inlineStr"/>
-      <c r="AG5" s="6" t="inlineStr"/>
+      <c r="AE5" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AF5" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AG5" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="AH5" s="6" t="inlineStr"/>
       <c r="AI5" s="6" t="inlineStr"/>
       <c r="AJ5" s="6" t="inlineStr"/>
@@ -37139,7 +37135,11 @@
       <c r="AL5" s="6" t="inlineStr"/>
       <c r="AM5" s="6" t="inlineStr"/>
       <c r="AN5" s="6" t="inlineStr"/>
-      <c r="AO5" s="6" t="inlineStr"/>
+      <c r="AO5" s="6" t="inlineStr">
+        <is>
+          <t>4.333</t>
+        </is>
+      </c>
       <c r="AP5" s="6" t="inlineStr"/>
       <c r="AQ5" s="6" t="inlineStr">
         <is>
@@ -37459,7 +37459,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>3.37</v>
+        <v>3.38</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
@@ -37597,7 +37597,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
@@ -38059,7 +38059,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
@@ -38387,7 +38387,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
@@ -38853,7 +38853,7 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
@@ -38991,7 +38991,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
@@ -39129,7 +39129,7 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
@@ -41413,17 +41413,17 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Igor Formiga</t>
+          <t>Lucas Mugni</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
@@ -41446,10 +41446,14 @@
           <t>04/01 6:30 PM</t>
         </is>
       </c>
-      <c r="J35" s="6" t="inlineStr"/>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>147148</t>
+        </is>
+      </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>Shots On Target</t>
+          <t>Assists</t>
         </is>
       </c>
       <c r="L35" s="6" t="inlineStr">
@@ -41459,7 +41463,7 @@
       </c>
       <c r="M35" s="6" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="N35" s="5" t="inlineStr">
@@ -41468,25 +41472,25 @@
         </is>
       </c>
       <c r="O35" s="6" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="P35" s="6" t="n">
         <v>-0.5</v>
       </c>
       <c r="Q35" s="6" t="n">
-        <v>0.0579</v>
+        <v>0.0569</v>
       </c>
       <c r="R35" s="6" t="n">
-        <v>-0.0613</v>
+        <v>-0.2121</v>
       </c>
       <c r="S35" s="6" t="n">
-        <v>0.3254</v>
+        <v>0.3391</v>
       </c>
       <c r="T35" s="6" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="U35" s="6" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="V35" s="6" t="inlineStr"/>
       <c r="W35" s="6" t="inlineStr"/>
@@ -41543,21 +41547,21 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Lucas Mugni</t>
+          <t>Igor Formiga</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
@@ -41580,11 +41584,7 @@
           <t>04/01 6:30 PM</t>
         </is>
       </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>147148</t>
-        </is>
-      </c>
+      <c r="J36" s="3" t="inlineStr"/>
       <c r="K36" s="3" t="inlineStr">
         <is>
           <t>Assists</t>
@@ -41681,7 +41681,7 @@
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
@@ -41721,7 +41721,7 @@
       <c r="J37" s="6" t="inlineStr"/>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>Assists</t>
+          <t>Shots On Target</t>
         </is>
       </c>
       <c r="L37" s="6" t="inlineStr">
@@ -41731,7 +41731,7 @@
       </c>
       <c r="M37" s="6" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="N37" s="5" t="inlineStr">
@@ -41740,25 +41740,25 @@
         </is>
       </c>
       <c r="O37" s="6" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="P37" s="6" t="n">
         <v>-0.5</v>
       </c>
       <c r="Q37" s="6" t="n">
-        <v>0.0569</v>
+        <v>0.0579</v>
       </c>
       <c r="R37" s="6" t="n">
-        <v>-0.2121</v>
+        <v>-0.0613</v>
       </c>
       <c r="S37" s="6" t="n">
-        <v>0.3391</v>
+        <v>0.3254</v>
       </c>
       <c r="T37" s="6" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="U37" s="6" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="V37" s="6" t="inlineStr"/>
       <c r="W37" s="6" t="inlineStr"/>
@@ -43129,7 +43129,7 @@
         </is>
       </c>
       <c r="B47" s="6" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
@@ -44419,7 +44419,7 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
@@ -45847,7 +45847,7 @@
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
@@ -45985,7 +45985,7 @@
         </is>
       </c>
       <c r="B67" s="6" t="n">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
